--- a/data/2025/17-dolj/69900-craiova/budget_file.xlsx
+++ b/data/2025/17-dolj/69900-craiova/budget_file.xlsx
@@ -551,9 +551,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="2">
-        <f>== SECTIUNEA FUNCTIONARE ===</f>
-        <v/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>=== SECTIUNEA FUNCTIONARE ===</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>961</v>
@@ -31547,9 +31548,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="2">
-        <f>== SECTIUNEA DEZVOLTARE ===</f>
-        <v/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>=== SECTIUNEA DEZVOLTARE ===</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>1546</v>
@@ -47890,9 +47892,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="2">
-        <f>===== SECTIUNEA TOTAL ======</f>
-        <v/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>====== SECTIUNEA TOTAL ======</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -48379,52 +48382,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>03.02</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Impozit pe venit(cod 03.02.17+03.02.18)</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n">
-        <v>9649</v>
-      </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>5581</v>
       </c>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n">
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
         <v>9900</v>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="P13" s="6" t="n">
         <v>10138</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell '.30500' in column total_2026; 03.02 total_2026: parent 0,00 != sum(children) 9.305,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -48449,7 +48452,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n">
-        <v>10138</v>
+        <v>9305</v>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n">
@@ -48469,7 +48472,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -91386,7 +91389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -91432,7 +91435,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -91445,74 +91448,74 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>00.11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 03.02 total_2026: sum now consistent — applied</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 00.03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00.02</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p1: 1 cells recovered</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00.11</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 00.03</t>
+          <t>unparseable cell '.30500' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -91520,65 +91523,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00.02</t>
+          <t>03.02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>03.02 total_2026: parent 0,00 != sum(children) 9.305,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>03.02</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>53</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>unparseable cell 'EXECUTIVADJ.,' in column est2027</t>
         </is>
@@ -91595,7 +91573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -91617,7 +91595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -91627,72 +91605,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1571</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1568</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>99.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12512</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12502</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5fe6935295dd89d3192874c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8a67f7fee04bdf30a73ebf9810e590b09c0806ad33fd109d319c88b7e70680a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL DETALIAT LA VENITURI PE CAPITOLE SI SUBCAPITOL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-53, 1615 linii</t>
         </is>
